--- a/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action - コピー\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C208232-351B-4777-949B-0D6BF3716033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA7EAF76-07BE-4E7A-A67E-FDE009C9FB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Platform" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -467,7 +467,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
@@ -492,27 +492,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -547,47 +547,47 @@
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
@@ -682,17 +682,17 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
@@ -712,7 +712,7 @@
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
@@ -722,7 +722,7 @@
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
@@ -742,7 +742,7 @@
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
@@ -752,47 +752,47 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
@@ -802,12 +802,12 @@
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
@@ -817,7 +817,7 @@
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
@@ -827,12 +827,12 @@
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
@@ -852,17 +852,17 @@
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
@@ -872,27 +872,27 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA7EAF76-07BE-4E7A-A67E-FDE009C9FB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9409372-0B7B-45C7-A32C-90617A7E9EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Platform" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -497,12 +497,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
@@ -517,92 +517,92 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">

--- a/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9409372-0B7B-45C7-A32C-90617A7E9EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1E03C5F-2E16-4FB6-A361-C9632858B0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Platform" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -567,42 +567,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">

--- a/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1E03C5F-2E16-4FB6-A361-C9632858B0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA45BF8B-A873-474B-B7C3-918B93D999BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="18000" windowHeight="9270" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Platform" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -572,12 +575,12 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">

--- a/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Platform.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA45BF8B-A873-474B-B7C3-918B93D999BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8144354F-2B59-45C8-9473-E23C6A59DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="18000" windowHeight="9270" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Platform" sheetId="1" r:id="rId1"/>
@@ -600,27 +600,27 @@
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
